--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
         <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-17.647058823529</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-17.391304347826</v>
+        <v>-8</v>
       </c>
       <c r="L16" s="14">
-        <v>-26.923076923076</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M16" s="14">
-        <v>-45.714285714285</v>
+        <v>-46.511627906976</v>
       </c>
       <c r="N16" s="14">
-        <v>-82.568807339449</v>
+        <v>-82.706766917293</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>-36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
+        <v>29</v>
+      </c>
+      <c r="G17" s="15">
         <v>25</v>
       </c>
-      <c r="G17" s="15">
-        <v>22</v>
-      </c>
       <c r="H17" s="14">
-        <v>13.636363636363</v>
+        <v>16</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J17" s="15">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K17" s="14">
-        <v>15.625</v>
+        <v>17.073170731707</v>
       </c>
       <c r="L17" s="14">
-        <v>19.354838709677</v>
+        <v>37.142857142857</v>
       </c>
       <c r="M17" s="14">
-        <v>164.285714285714</v>
+        <v>220</v>
       </c>
       <c r="N17" s="14">
-        <v>-2.631578947368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>-45.454545454545</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="M18" s="14">
-        <v>-76.923076923076</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.052631578947</v>
+        <v>-95.930232558139</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F19" s="15">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>-13.157894736842</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="I19" s="15">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J19" s="15">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.843137254901</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L19" s="14">
-        <v>-12.962962962963</v>
+        <v>-18.75</v>
       </c>
       <c r="M19" s="14">
-        <v>42.424242424242</v>
+        <v>40.540540540540</v>
       </c>
       <c r="N19" s="14">
-        <v>-22.950819672131</v>
+        <v>-26.760563380281</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G20" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="14">
-        <v>-10.526315789473</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L20" s="14">
-        <v>-41.176470588235</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M20" s="14">
-        <v>-14.285714285714</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.167101827676</v>
+        <v>-93.013100436681</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.75</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G21" s="17">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.737864077669</v>
+        <v>-9.183673469387</v>
       </c>
       <c r="I21" s="17">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="J21" s="17">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.083333333333</v>
+        <v>-6.285714285714</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.229050279329</v>
+        <v>-17.587939698492</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.758620689655</v>
+        <v>-0.606060606060</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.274900398406</v>
+        <v>-81.489841986456</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E24" s="14">
-        <v>-35.714285714285</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="F24" s="15">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="G24" s="15">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H24" s="14">
-        <v>7.407407407407</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="I24" s="15">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J24" s="15">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="K24" s="14">
-        <v>5.072463768115</v>
+        <v>-2.395209580838</v>
       </c>
       <c r="L24" s="14">
-        <v>20.833333333333</v>
+        <v>15.602836879432</v>
       </c>
       <c r="M24" s="14">
-        <v>126.5625</v>
+        <v>117.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E25" s="14">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="15">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G25" s="15">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H25" s="14">
-        <v>19.230769230769</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="I25" s="15">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="J25" s="15">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="K25" s="14">
-        <v>7.246376811594</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>34.545454545454</v>
+        <v>35.9375</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-8.333333333333</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G26" s="15">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>-17.777777777777</v>
+        <v>17.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="J26" s="15">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K26" s="14">
-        <v>-8.474576271186</v>
+        <v>4.615384615384</v>
       </c>
       <c r="L26" s="14">
-        <v>-1.818181818181</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>20</v>
+        <v>19.298245614035</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
+        <v>100</v>
+      </c>
+      <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
         <v>0</v>
       </c>
-      <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15">
-        <v>3</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-33.333333333333</v>
-      </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -904,11 +904,11 @@
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>87.5</v>
+        <v>81.818181818181</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>-8</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L16" s="14">
-        <v>-20.689655172413</v>
+        <v>0</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.511627906976</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N16" s="14">
-        <v>-82.706766917293</v>
+        <v>-79.591836734693</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H17" s="14">
-        <v>16</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="I17" s="15">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J17" s="15">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K17" s="14">
-        <v>17.073170731707</v>
+        <v>3.921568627450</v>
       </c>
       <c r="L17" s="14">
-        <v>37.142857142857</v>
+        <v>26.190476190476</v>
       </c>
       <c r="M17" s="14">
-        <v>220</v>
+        <v>194.444444444444</v>
       </c>
       <c r="N17" s="14">
-        <v>20</v>
+        <v>15.217391304347</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="15">
         <v>3</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="15">
-        <v>4</v>
       </c>
       <c r="G18" s="15">
         <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-42.857142857142</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K18" s="14">
         <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>-56.25</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M18" s="14">
-        <v>-74.074074074074</v>
+        <v>-75.757575757575</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.930232558139</v>
+        <v>-96.097560975609</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-54.545454545454</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" s="14">
-        <v>-24.324324324324</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I19" s="15">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J19" s="15">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K19" s="14">
-        <v>-16.129032258064</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L19" s="14">
-        <v>-18.75</v>
+        <v>-17.5</v>
       </c>
       <c r="M19" s="14">
-        <v>40.540540540540</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N19" s="14">
-        <v>-26.760563380281</v>
+        <v>-19.512195121951</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D20" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G20" s="15">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H20" s="14">
-        <v>-40</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="I20" s="15">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J20" s="15">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K20" s="14">
-        <v>3.225806451612</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-38.461538461538</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="M20" s="14">
-        <v>-17.948717948717</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.013100436681</v>
+        <v>-92.164179104477</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.258064516129</v>
+        <v>15.151515151515</v>
       </c>
       <c r="F21" s="17">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.183673469387</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I21" s="17">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="J21" s="17">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.285714285714</v>
+        <v>-3.365384615384</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.587939698492</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.606060606060</v>
+        <v>5.789473684210</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.489841986456</v>
+        <v>-80.466472303207</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-34.482758620689</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G24" s="15">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H24" s="14">
-        <v>-7.843137254901</v>
+        <v>-19.811320754717</v>
       </c>
       <c r="I24" s="15">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="J24" s="15">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K24" s="14">
-        <v>-2.395209580838</v>
+        <v>-4.787234042553</v>
       </c>
       <c r="L24" s="14">
-        <v>15.602836879432</v>
+        <v>13.291139240506</v>
       </c>
       <c r="M24" s="14">
-        <v>117.333333333333</v>
+        <v>110.588235294118</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G25" s="15">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H25" s="14">
-        <v>-8.928571428571</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="I25" s="15">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J25" s="15">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="K25" s="14">
-        <v>-3.333333333333</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="L25" s="14">
-        <v>35.9375</v>
+        <v>37.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>133.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>17.142857142857</v>
+        <v>19.444444444444</v>
       </c>
       <c r="I26" s="15">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J26" s="15">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K26" s="14">
-        <v>4.615384615384</v>
+        <v>2.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>13.333333333333</v>
+        <v>14.925373134328</v>
       </c>
       <c r="M26" s="14">
-        <v>19.298245614035</v>
+        <v>13.235294117647</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,22 +1394,22 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,37 +854,37 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
         <v>-100</v>
       </c>
+      <c r="L14" s="15">
+        <v>-100</v>
+      </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -901,7 +901,7 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
@@ -910,228 +910,228 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <v>2</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>2</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>0</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>-50</v>
       </c>
-      <c r="N15" s="14">
-        <v>-66.666666666666</v>
+      <c r="N15" s="15">
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>7</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>133.333333333333</v>
-      </c>
-      <c r="F16" s="15">
-        <v>20</v>
-      </c>
-      <c r="G16" s="15">
-        <v>11</v>
-      </c>
-      <c r="H16" s="14">
-        <v>81.818181818181</v>
-      </c>
-      <c r="I16" s="15">
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>18</v>
+      </c>
+      <c r="G16" s="14">
+        <v>10</v>
+      </c>
+      <c r="H16" s="15">
+        <v>80</v>
+      </c>
+      <c r="I16" s="14">
+        <v>31</v>
+      </c>
+      <c r="J16" s="14">
         <v>30</v>
       </c>
-      <c r="J16" s="15">
-        <v>28</v>
-      </c>
-      <c r="K16" s="14">
-        <v>7.142857142857</v>
-      </c>
-      <c r="L16" s="14">
-        <v>0</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-41.176470588235</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-79.591836734693</v>
+      <c r="K16" s="15">
+        <v>3.333333333333</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-11.428571428571</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-39.215686274509</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-81.656804733727</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>5</v>
-      </c>
-      <c r="D17" s="15">
-        <v>10</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F17" s="15">
-        <v>28</v>
-      </c>
-      <c r="G17" s="15">
-        <v>33</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-15.151515151515</v>
-      </c>
-      <c r="I17" s="15">
-        <v>53</v>
-      </c>
-      <c r="J17" s="15">
-        <v>51</v>
-      </c>
-      <c r="K17" s="14">
-        <v>3.921568627450</v>
-      </c>
-      <c r="L17" s="14">
-        <v>26.190476190476</v>
-      </c>
-      <c r="M17" s="14">
-        <v>194.444444444444</v>
-      </c>
-      <c r="N17" s="14">
-        <v>15.217391304347</v>
+      <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
+        <v>7</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="F17" s="14">
+        <v>24</v>
+      </c>
+      <c r="G17" s="14">
+        <v>37</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-35.135135135135</v>
+      </c>
+      <c r="I17" s="14">
+        <v>57</v>
+      </c>
+      <c r="J17" s="14">
+        <v>58</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-1.724137931034</v>
+      </c>
+      <c r="L17" s="15">
+        <v>11.764705882352</v>
+      </c>
+      <c r="M17" s="15">
+        <v>171.428571428571</v>
+      </c>
+      <c r="N17" s="15">
+        <v>3.636363636363</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="G18" s="15">
-        <v>7</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="G18" s="14">
+        <v>9</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I18" s="14">
         <v>8</v>
       </c>
-      <c r="J18" s="15">
-        <v>16</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-52.941176470588</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-75.757575757575</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-96.097560975609</v>
+      <c r="J18" s="14">
+        <v>20</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-80.487804878048</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-96.412556053811</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>14</v>
-      </c>
-      <c r="D19" s="15">
-        <v>7</v>
-      </c>
-      <c r="E19" s="14">
-        <v>100</v>
-      </c>
-      <c r="F19" s="15">
-        <v>31</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
         <v>36</v>
       </c>
-      <c r="H19" s="14">
-        <v>-13.888888888888</v>
-      </c>
-      <c r="I19" s="15">
-        <v>66</v>
-      </c>
-      <c r="J19" s="15">
-        <v>69</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-4.347826086956</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-17.5</v>
-      </c>
-      <c r="M19" s="14">
-        <v>57.142857142857</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-19.512195121951</v>
+      <c r="G19" s="14">
+        <v>36</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14">
+        <v>75</v>
+      </c>
+      <c r="J19" s="14">
+        <v>77</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-2.597402597402</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="M19" s="15">
+        <v>53.061224489795</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-18.478260869565</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>11</v>
-      </c>
-      <c r="D20" s="15">
-        <v>11</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>8</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="F20" s="14">
         <v>17</v>
       </c>
-      <c r="G20" s="15">
-        <v>29</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-41.379310344827</v>
-      </c>
-      <c r="I20" s="15">
-        <v>42</v>
-      </c>
-      <c r="J20" s="15">
-        <v>42</v>
-      </c>
-      <c r="K20" s="14">
-        <v>0</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-28.813559322033</v>
-      </c>
-      <c r="M20" s="14">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-92.164179104477</v>
+      <c r="G20" s="14">
+        <v>33</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-48.484848484848</v>
+      </c>
+      <c r="I20" s="14">
+        <v>44</v>
+      </c>
+      <c r="J20" s="14">
+        <v>50</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-12</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-29.032258064516</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-4.347826086956</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-92.775041050903</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>15.151515151515</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.793103448275</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.365384615384</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.987012987013</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="M21" s="18">
-        <v>5.789473684210</v>
+        <v>2.358490566037</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.466472303207</v>
+        <v>-81.325301204819</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,7 +1188,7 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
@@ -1197,7 +1197,7 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="14">
         <v>2</v>
       </c>
       <c r="J22" s="13" t="s">
@@ -1206,11 +1206,11 @@
       <c r="K22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-50</v>
+      <c r="L22" s="15">
+        <v>-60</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-60</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>15</v>
-      </c>
-      <c r="D24" s="15">
-        <v>21</v>
-      </c>
-      <c r="E24" s="14">
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>28</v>
+      </c>
+      <c r="E24" s="15">
         <v>-28.571428571428</v>
       </c>
-      <c r="F24" s="15">
-        <v>85</v>
-      </c>
-      <c r="G24" s="15">
+      <c r="F24" s="14">
+        <v>76</v>
+      </c>
+      <c r="G24" s="14">
         <v>106</v>
       </c>
-      <c r="H24" s="14">
-        <v>-19.811320754717</v>
-      </c>
-      <c r="I24" s="15">
-        <v>179</v>
-      </c>
-      <c r="J24" s="15">
-        <v>188</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-4.787234042553</v>
-      </c>
-      <c r="L24" s="14">
-        <v>13.291139240506</v>
-      </c>
-      <c r="M24" s="14">
-        <v>110.588235294118</v>
+      <c r="H24" s="15">
+        <v>-28.301886792452</v>
+      </c>
+      <c r="I24" s="14">
+        <v>201</v>
+      </c>
+      <c r="J24" s="14">
+        <v>216</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-6.944444444444</v>
+      </c>
+      <c r="L24" s="15">
+        <v>5.789473684210</v>
+      </c>
+      <c r="M24" s="15">
+        <v>97.058823529411</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>8</v>
-      </c>
-      <c r="D25" s="15">
-        <v>16</v>
-      </c>
-      <c r="E25" s="14">
+      <c r="C25" s="14">
+        <v>7</v>
+      </c>
+      <c r="D25" s="14">
+        <v>14</v>
+      </c>
+      <c r="E25" s="15">
         <v>-50</v>
       </c>
-      <c r="F25" s="15">
-        <v>46</v>
-      </c>
-      <c r="G25" s="15">
-        <v>63</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-26.984126984127</v>
-      </c>
-      <c r="I25" s="15">
-        <v>96</v>
-      </c>
-      <c r="J25" s="15">
-        <v>106</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-9.433962264150</v>
-      </c>
-      <c r="L25" s="14">
-        <v>37.142857142857</v>
+      <c r="F25" s="14">
+        <v>35</v>
+      </c>
+      <c r="G25" s="14">
+        <v>61</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-42.622950819672</v>
+      </c>
+      <c r="I25" s="14">
+        <v>103</v>
+      </c>
+      <c r="J25" s="14">
+        <v>120</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-14.166666666666</v>
+      </c>
+      <c r="L25" s="15">
+        <v>25.609756097561</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>10</v>
-      </c>
-      <c r="D26" s="15">
-        <v>10</v>
-      </c>
-      <c r="E26" s="14">
-        <v>0</v>
-      </c>
-      <c r="F26" s="15">
-        <v>43</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C26" s="14">
+        <v>9</v>
+      </c>
+      <c r="D26" s="14">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="F26" s="14">
+        <v>42</v>
+      </c>
+      <c r="G26" s="14">
         <v>36</v>
       </c>
-      <c r="H26" s="14">
-        <v>19.444444444444</v>
-      </c>
-      <c r="I26" s="15">
-        <v>77</v>
-      </c>
-      <c r="J26" s="15">
-        <v>75</v>
-      </c>
-      <c r="K26" s="14">
-        <v>2.666666666666</v>
-      </c>
-      <c r="L26" s="14">
-        <v>14.925373134328</v>
-      </c>
-      <c r="M26" s="14">
-        <v>13.235294117647</v>
+      <c r="H26" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="I26" s="14">
+        <v>84</v>
+      </c>
+      <c r="J26" s="14">
+        <v>83</v>
+      </c>
+      <c r="K26" s="15">
+        <v>1.204819277108</v>
+      </c>
+      <c r="L26" s="15">
+        <v>10.526315789473</v>
+      </c>
+      <c r="M26" s="15">
+        <v>12</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,34 +1384,34 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>100</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>3</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="15">
         <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I28" s="15">
-        <v>7</v>
-      </c>
-      <c r="J28" s="15">
-        <v>7</v>
-      </c>
-      <c r="K28" s="14">
+      <c r="H28" s="15">
+        <v>25</v>
+      </c>
+      <c r="I28" s="14">
+        <v>8</v>
+      </c>
+      <c r="J28" s="14">
+        <v>8</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="14">
-        <v>-22.222222222222</v>
+      <c r="L28" s="15">
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,10 +1496,10 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-100</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-100</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>15</v>
       </c>
-      <c r="E39" s="15">
-        <v>21</v>
-      </c>
-      <c r="G39" s="15">
+      <c r="E39" s="14">
+        <v>21</v>
+      </c>
+      <c r="G39" s="14">
         <v>7</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>4</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>3</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-25</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-57.142857142857</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-85.714285714285</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-80</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>31</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>33</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>40</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>19</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>17</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-10.526315789473</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-57.5</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-48.484848484848</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-45.161290322580</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>832</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>891</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>545</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>344</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>196</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-43.023255813953</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-64.036697247706</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-78.002244668911</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-76.442307692307</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>329</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>408</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>297</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>241</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>360</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>49.377593360995</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>21.212121212121</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-11.764705882352</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>9.422492401215</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1348</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1230</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>662</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>417</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>118</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-71.702637889688</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-82.175226586102</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-90.406504065040</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-91.246290801186</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>715</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>595</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>440</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>381</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>554</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>45.406824146981</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>25.909090909090</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-6.890756302521</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-22.517482517482</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>3071</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>3304</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>1370</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>778</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>391</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-49.742930591259</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-71.459854014598</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-88.165859564164</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-87.267990882448</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -895,35 +895,35 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N15" s="15">
         <v>-71.428571428571</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
         <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>3.333333333333</v>
+        <v>6.060606060606</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.428571428571</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.215686274509</v>
+        <v>-35.185185185185</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.656804733727</v>
+        <v>-81.283422459893</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>350</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.135135135135</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I17" s="14">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J17" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.724137931034</v>
+        <v>10</v>
       </c>
       <c r="L17" s="15">
-        <v>11.764705882352</v>
+        <v>13.793103448275</v>
       </c>
       <c r="M17" s="15">
-        <v>171.428571428571</v>
+        <v>164</v>
       </c>
       <c r="N17" s="15">
-        <v>3.636363636363</v>
+        <v>13.793103448275</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
         <v>4</v>
       </c>
-      <c r="E18" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>3</v>
-      </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-60</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L18" s="15">
-        <v>-55.555555555555</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.487804878048</v>
+        <v>-78.260869565217</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.412556053811</v>
+        <v>-95.918367346938</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
         <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>162.5</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>41.176470588235</v>
       </c>
       <c r="I19" s="14">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.597402597402</v>
+        <v>12.941176470588</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.666666666666</v>
+        <v>-4</v>
       </c>
       <c r="M19" s="15">
-        <v>53.061224489795</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.478260869565</v>
+        <v>-5.882352941176</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-62.5</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-48.484848484848</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K20" s="15">
-        <v>-12</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.032258064516</v>
+        <v>-20.3125</v>
       </c>
       <c r="M20" s="15">
-        <v>-4.347826086956</v>
+        <v>6.25</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.775041050903</v>
+        <v>-92.319277108433</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>95.454545454545</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="G21" s="17">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.428571428571</v>
+        <v>0.862068965517</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="J21" s="17">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.823529411764</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.216216216216</v>
+        <v>-9.407665505226</v>
       </c>
       <c r="M21" s="18">
-        <v>2.358490566037</v>
+        <v>12.068965517241</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.325301204819</v>
+        <v>-79.527559055118</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.571428571428</v>
+        <v>38.888888888888</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.301886792452</v>
+        <v>-17.708333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="J24" s="14">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.944444444444</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L24" s="15">
-        <v>5.789473684210</v>
+        <v>5.633802816901</v>
       </c>
       <c r="M24" s="15">
-        <v>97.058823529411</v>
+        <v>85.950413223140</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.622950819672</v>
+        <v>-35.087719298245</v>
       </c>
       <c r="I25" s="14">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="J25" s="14">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.166666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L25" s="15">
-        <v>25.609756097561</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
         <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I26" s="14">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K26" s="15">
-        <v>1.204819277108</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="L26" s="15">
-        <v>10.526315789473</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="M26" s="15">
-        <v>12</v>
+        <v>10.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
         <v>-11.111111111111</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-60</v>
+        <v>-62.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>6.060606060606</v>
+        <v>2.702702702702</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.894736842105</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.185185185185</v>
+        <v>-37.704918032786</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.283422459893</v>
+        <v>-81.372549019607</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K17" s="15">
-        <v>10</v>
+        <v>12.307692307692</v>
       </c>
       <c r="L17" s="15">
-        <v>13.793103448275</v>
+        <v>19.672131147541</v>
       </c>
       <c r="M17" s="15">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="N17" s="15">
-        <v>13.793103448275</v>
+        <v>10.606060606060</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.636363636363</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="I18" s="14">
         <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>-54.545454545454</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="L18" s="15">
-        <v>-56.521739130434</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.260869565217</v>
+        <v>-81.132075471698</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.918367346938</v>
+        <v>-96.323529411764</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>162.5</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>41.176470588235</v>
+        <v>93.75</v>
       </c>
       <c r="I19" s="14">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K19" s="15">
-        <v>12.941176470588</v>
+        <v>22.340425531914</v>
       </c>
       <c r="L19" s="15">
-        <v>-4</v>
+        <v>1.769911504424</v>
       </c>
       <c r="M19" s="15">
-        <v>77.777777777777</v>
+        <v>91.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-5.882352941176</v>
+        <v>-2.542372881355</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>60</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20" s="14">
         <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-23.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J20" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.272727272727</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.3125</v>
+        <v>-18.840579710144</v>
       </c>
       <c r="M20" s="15">
-        <v>6.25</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.319277108433</v>
+        <v>-92.112676056338</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>95.454545454545</v>
+        <v>20.689655172413</v>
       </c>
       <c r="F21" s="17">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H21" s="18">
-        <v>0.862068965517</v>
+        <v>14.912280701754</v>
       </c>
       <c r="I21" s="17">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="J21" s="17">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>2.076124567474</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.407665505226</v>
+        <v>-6.940063091482</v>
       </c>
       <c r="M21" s="18">
-        <v>12.068965517241</v>
+        <v>13.899613899613</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.527559055118</v>
+        <v>-78.684971098265</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>38.888888888888</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-17.708333333333</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="I24" s="14">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="J24" s="14">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.846153846153</v>
+        <v>-3.501945525291</v>
       </c>
       <c r="L24" s="15">
-        <v>5.633802816901</v>
+        <v>4.641350210970</v>
       </c>
       <c r="M24" s="15">
-        <v>85.950413223140</v>
+        <v>87.878787878787</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.087719298245</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="14">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="J25" s="14">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.111111111111</v>
+        <v>-12.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>23.076923076923</v>
+        <v>9.821428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>11.111111111111</v>
+        <v>2.325581395348</v>
       </c>
       <c r="I26" s="14">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="J26" s="14">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.105263157894</v>
+        <v>0.925925925925</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.105263157894</v>
+        <v>2.830188679245</v>
       </c>
       <c r="M26" s="15">
-        <v>10.714285714285</v>
+        <v>19.780219780219</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I28" s="14">
+        <v>9</v>
+      </c>
+      <c r="J28" s="14">
+        <v>10</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-10</v>
+      </c>
+      <c r="L28" s="15">
         <v>0</v>
-      </c>
-      <c r="I28" s="14">
-        <v>8</v>
-      </c>
-      <c r="J28" s="14">
-        <v>9</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-11.111111111111</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
         <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>2.702702702702</v>
+        <v>2.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.391304347826</v>
+        <v>-14.583333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.704918032786</v>
+        <v>-35.9375</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.372549019607</v>
+        <v>-81.858407079646</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I17" s="14">
+        <v>81</v>
+      </c>
+      <c r="J17" s="14">
         <v>73</v>
       </c>
-      <c r="J17" s="14">
-        <v>65</v>
-      </c>
       <c r="K17" s="15">
-        <v>12.307692307692</v>
+        <v>10.958904109589</v>
       </c>
       <c r="L17" s="15">
-        <v>19.672131147541</v>
+        <v>14.084507042253</v>
       </c>
       <c r="M17" s="15">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N17" s="15">
-        <v>10.606060606060</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-76.923076923076</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-62.962962962963</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.333333333333</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.132075471698</v>
+        <v>-82.8125</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.323529411764</v>
+        <v>-96.167247386759</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>111.111111111111</v>
+        <v>240</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>93.75</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I19" s="14">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="J19" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>22.340425531914</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>1.769911504424</v>
+        <v>12.820512820512</v>
       </c>
       <c r="M19" s="15">
-        <v>91.666666666666</v>
+        <v>106.25</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.542372881355</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>6</v>
-      </c>
       <c r="E20" s="15">
-        <v>-16.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J20" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.196721311475</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.840579710144</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="15">
-        <v>7.692307692307</v>
+        <v>10.344827586206</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.112676056338</v>
+        <v>-91.500664010624</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>20.689655172413</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G21" s="17">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H21" s="18">
-        <v>14.912280701754</v>
+        <v>28.155339805825</v>
       </c>
       <c r="I21" s="17">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="J21" s="17">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="K21" s="18">
-        <v>2.076124567474</v>
+        <v>7.073954983922</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.940063091482</v>
+        <v>-2.346041055718</v>
       </c>
       <c r="M21" s="18">
-        <v>13.899613899613</v>
+        <v>16.842105263157</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.684971098265</v>
+        <v>-77.560646900269</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.347826086956</v>
+        <v>-62.5</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.888888888888</v>
+        <v>-20.792079207920</v>
       </c>
       <c r="I24" s="14">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="J24" s="14">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.501945525291</v>
+        <v>-9.688581314878</v>
       </c>
       <c r="L24" s="15">
-        <v>4.641350210970</v>
+        <v>-1.879699248120</v>
       </c>
       <c r="M24" s="15">
-        <v>87.878787878787</v>
+        <v>85.106382978723</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.428571428571</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>-30</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="I25" s="14">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J25" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.142857142857</v>
+        <v>-18.709677419354</v>
       </c>
       <c r="L25" s="15">
-        <v>9.821428571428</v>
+        <v>0.8</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>2.325581395348</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I26" s="14">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J26" s="14">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K26" s="15">
-        <v>0.925925925925</v>
+        <v>1.709401709401</v>
       </c>
       <c r="L26" s="15">
-        <v>2.830188679245</v>
+        <v>1.709401709401</v>
       </c>
       <c r="M26" s="15">
-        <v>19.780219780219</v>
+        <v>20.202020202020</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
+        <v>11</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0</v>
+      </c>
+      <c r="L28" s="15">
         <v>10</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-10</v>
-      </c>
-      <c r="L28" s="15">
-        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>13</v>
+      </c>
+      <c r="G16" s="14">
+        <v>14</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-7.142857142857</v>
+      </c>
+      <c r="I16" s="14">
+        <v>44</v>
+      </c>
+      <c r="J16" s="14">
+        <v>44</v>
+      </c>
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>11</v>
-      </c>
-      <c r="G16" s="14">
-        <v>12</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-8.333333333333</v>
-      </c>
-      <c r="I16" s="14">
-        <v>41</v>
-      </c>
-      <c r="J16" s="14">
-        <v>40</v>
-      </c>
-      <c r="K16" s="15">
-        <v>2.5</v>
-      </c>
       <c r="L16" s="15">
-        <v>-14.583333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.9375</v>
+        <v>-34.328358208955</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.858407079646</v>
+        <v>-82.539682539682</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>22.727272727272</v>
+        <v>40</v>
       </c>
       <c r="I17" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J17" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K17" s="15">
-        <v>10.958904109589</v>
+        <v>8.974358974358</v>
       </c>
       <c r="L17" s="15">
-        <v>14.084507042253</v>
+        <v>4.938271604938</v>
       </c>
       <c r="M17" s="15">
-        <v>200</v>
+        <v>193.103448275862</v>
       </c>
       <c r="N17" s="15">
-        <v>8</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>-60.714285714285</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="L18" s="15">
-        <v>-60.714285714285</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="M18" s="15">
-        <v>-82.8125</v>
+        <v>-79.104477611940</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.167247386759</v>
+        <v>-95.569620253164</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>240</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F19" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>116.666666666667</v>
+        <v>74.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J19" s="14">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K19" s="15">
-        <v>33.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L19" s="15">
-        <v>12.820512820512</v>
+        <v>7.936507936507</v>
       </c>
       <c r="M19" s="15">
-        <v>106.25</v>
+        <v>94.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>3.125</v>
+        <v>-2.158273381294</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>60</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J20" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.030303030303</v>
+        <v>-9.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.111111111111</v>
+        <v>-11.688311688311</v>
       </c>
       <c r="M20" s="15">
-        <v>10.344827586206</v>
+        <v>3.030303030303</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.500664010624</v>
+        <v>-91.933570581257</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>72.727272727272</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="F21" s="17">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G21" s="17">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>28.155339805825</v>
+        <v>27.619047619047</v>
       </c>
       <c r="I21" s="17">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="J21" s="17">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="K21" s="18">
-        <v>7.073954983922</v>
+        <v>2.332361516034</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.346041055718</v>
+        <v>-5.645161290322</v>
       </c>
       <c r="M21" s="18">
-        <v>16.842105263157</v>
+        <v>14.332247557003</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.560646900269</v>
+        <v>-78.714372346876</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-62.5</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.792079207920</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="J24" s="14">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.688581314878</v>
+        <v>-15.264797507788</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.879699248120</v>
+        <v>-6.529209621993</v>
       </c>
       <c r="M24" s="15">
-        <v>85.106382978723</v>
+        <v>78.947368421052</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
         <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.775510204081</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="14">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J25" s="14">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.709677419354</v>
+        <v>-19.411764705882</v>
       </c>
       <c r="L25" s="15">
-        <v>0.8</v>
+        <v>-2.836879432624</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
         <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>4.761904761904</v>
+        <v>7.317073170731</v>
       </c>
       <c r="I26" s="14">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J26" s="14">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>1.709401709401</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L26" s="15">
-        <v>1.709401709401</v>
+        <v>1.587301587301</v>
       </c>
       <c r="M26" s="15">
-        <v>20.202020202020</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L28" s="15">
         <v>10</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>7</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
         <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>8.510638297872</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.384615384615</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.328358208955</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.539682539682</v>
+        <v>-80.970149253731</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>40</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I17" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>8.974358974358</v>
+        <v>9.638554216867</v>
       </c>
       <c r="L17" s="15">
-        <v>4.938271604938</v>
+        <v>4.597701149425</v>
       </c>
       <c r="M17" s="15">
-        <v>193.103448275862</v>
+        <v>184.375</v>
       </c>
       <c r="N17" s="15">
-        <v>6.25</v>
+        <v>8.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="E18" s="15">
-        <v>200</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.444444444444</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
         <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.724137931034</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="L18" s="15">
-        <v>-54.838709677419</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.104477611940</v>
+        <v>-79.452054794520</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.569620253164</v>
+        <v>-95.495495495495</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>-61.538461538461</v>
+        <v>1700</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>74.285714285714</v>
+        <v>107.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J19" s="14">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>21.428571428571</v>
+        <v>36.283185840708</v>
       </c>
       <c r="L19" s="15">
-        <v>7.936507936507</v>
+        <v>12.408759124087</v>
       </c>
       <c r="M19" s="15">
-        <v>94.285714285714</v>
+        <v>105.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.158273381294</v>
+        <v>6.206896551724</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>9</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>9</v>
-      </c>
       <c r="E20" s="15">
-        <v>-55.555555555555</v>
+        <v>125</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J20" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.333333333333</v>
+        <v>-2.531645569620</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.688311688311</v>
+        <v>-2.531645569620</v>
       </c>
       <c r="M20" s="15">
-        <v>3.030303030303</v>
+        <v>6.944444444444</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.933570581257</v>
+        <v>-91.482300884955</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-38.709677419354</v>
+        <v>223.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H21" s="18">
-        <v>27.619047619047</v>
+        <v>38.541666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="J21" s="17">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="K21" s="18">
-        <v>2.332361516034</v>
+        <v>10.393258426966</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.645161290322</v>
+        <v>0.255102040816</v>
       </c>
       <c r="M21" s="18">
-        <v>14.332247557003</v>
+        <v>18.373493975903</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.714372346876</v>
+        <v>-77.581289218482</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-64.516129032258</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-31.428571428571</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="J24" s="14">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.264797507788</v>
+        <v>-13.742690058479</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.529209621993</v>
+        <v>-3.908794788273</v>
       </c>
       <c r="M24" s="15">
-        <v>78.947368421052</v>
+        <v>85.534591194968</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-26.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H25" s="15">
-        <v>-30</v>
+        <v>-35.849056603773</v>
       </c>
       <c r="I25" s="14">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J25" s="14">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="K25" s="15">
-        <v>-19.411764705882</v>
+        <v>-18.435754189944</v>
       </c>
       <c r="L25" s="15">
-        <v>-2.836879432624</v>
+        <v>-1.351351351351</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="D26" s="14">
-        <v>8</v>
-      </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>7.317073170731</v>
+        <v>23.684210526315</v>
       </c>
       <c r="I26" s="14">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K26" s="15">
-        <v>3.225806451612</v>
+        <v>6.015037593984</v>
       </c>
       <c r="L26" s="15">
-        <v>1.587301587301</v>
+        <v>4.444444444444</v>
       </c>
       <c r="M26" s="15">
-        <v>14.285714285714</v>
+        <v>10.15625</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
         <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>14.285714285714</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J16" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K16" s="15">
-        <v>8.510638297872</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L16" s="15">
-        <v>-3.773584905660</v>
+        <v>3.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-28.169014084507</v>
+        <v>-22.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.970149253731</v>
+        <v>-79.285714285714</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>8</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>8.695652173913</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J17" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K17" s="15">
-        <v>9.638554216867</v>
+        <v>11.235955056179</v>
       </c>
       <c r="L17" s="15">
-        <v>4.597701149425</v>
+        <v>5.319148936170</v>
       </c>
       <c r="M17" s="15">
-        <v>184.375</v>
+        <v>191.176470588235</v>
       </c>
       <c r="N17" s="15">
-        <v>8.333333333333</v>
+        <v>7.608695652173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>125</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.275862068965</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.612903225806</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.452054794520</v>
+        <v>-74.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.495495495495</v>
+        <v>-94.586894586894</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>1700</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
         <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>107.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="K19" s="15">
-        <v>36.283185840708</v>
+        <v>33.606557377049</v>
       </c>
       <c r="L19" s="15">
-        <v>12.408759124087</v>
+        <v>11.643835616438</v>
       </c>
       <c r="M19" s="15">
-        <v>105.333333333333</v>
+        <v>103.75</v>
       </c>
       <c r="N19" s="15">
-        <v>6.206896551724</v>
+        <v>5.844155844155</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>125</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>8.333333333333</v>
+        <v>16</v>
       </c>
       <c r="I20" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J20" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K20" s="15">
-        <v>-2.531645569620</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="L20" s="15">
-        <v>-2.531645569620</v>
+        <v>1.190476190476</v>
       </c>
       <c r="M20" s="15">
-        <v>6.944444444444</v>
+        <v>6.25</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.482300884955</v>
+        <v>-91.219008264462</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>223.076923076923</v>
+        <v>27.586206896551</v>
       </c>
       <c r="F21" s="17">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G21" s="17">
         <v>96</v>
       </c>
       <c r="H21" s="18">
-        <v>38.541666666666</v>
+        <v>39.583333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="J21" s="17">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="K21" s="18">
-        <v>10.393258426966</v>
+        <v>11.688311688311</v>
       </c>
       <c r="L21" s="18">
-        <v>0.255102040816</v>
+        <v>2.137767220902</v>
       </c>
       <c r="M21" s="18">
-        <v>18.373493975903</v>
+        <v>21.813031161473</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.581289218482</v>
+        <v>-76.931330472103</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>9.523809523809</v>
+        <v>52.631578947368</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-36.111111111111</v>
+        <v>-27.884615384615</v>
       </c>
       <c r="I24" s="14">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="J24" s="14">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.742690058479</v>
+        <v>-10.249307479224</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.908794788273</v>
+        <v>-2.994011976047</v>
       </c>
       <c r="M24" s="15">
-        <v>85.534591194968</v>
+        <v>90.588235294117</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F25" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.849056603773</v>
+        <v>-34</v>
       </c>
       <c r="I25" s="14">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="J25" s="14">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.435754189944</v>
+        <v>-17.894736842105</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.351351351351</v>
+        <v>-2.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>14</v>
+      </c>
+      <c r="D26" s="14">
         <v>13</v>
       </c>
-      <c r="D26" s="14">
-        <v>9</v>
-      </c>
       <c r="E26" s="15">
-        <v>44.444444444444</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
         <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>23.684210526315</v>
+        <v>18.421052631578</v>
       </c>
       <c r="I26" s="14">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J26" s="14">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K26" s="15">
-        <v>6.015037593984</v>
+        <v>5.479452054794</v>
       </c>
       <c r="L26" s="15">
-        <v>4.444444444444</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M26" s="15">
-        <v>10.15625</v>
+        <v>12.408759124087</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1403,16 +1403,16 @@
         <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
@@ -1444,16 +1444,16 @@
         <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
         <v>50</v>
@@ -926,7 +926,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J16" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K16" s="15">
-        <v>11.538461538461</v>
+        <v>12.962962962963</v>
       </c>
       <c r="L16" s="15">
-        <v>3.571428571428</v>
+        <v>1.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.666666666666</v>
+        <v>-21.794871794871</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.285714285714</v>
+        <v>-79.180887372013</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14">
         <v>8</v>
       </c>
-      <c r="D17" s="14">
-        <v>6</v>
-      </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>4.166666666666</v>
+        <v>17.391304347826</v>
       </c>
       <c r="I17" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J17" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K17" s="15">
-        <v>11.235955056179</v>
+        <v>12.371134020618</v>
       </c>
       <c r="L17" s="15">
-        <v>5.319148936170</v>
+        <v>9</v>
       </c>
       <c r="M17" s="15">
-        <v>191.176470588235</v>
+        <v>194.594594594595</v>
       </c>
       <c r="N17" s="15">
-        <v>7.608695652173</v>
+        <v>10.101010101010</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="15">
         <v>100</v>
       </c>
-      <c r="F18" s="14">
-        <v>9</v>
-      </c>
-      <c r="G18" s="14">
-        <v>4</v>
-      </c>
-      <c r="H18" s="15">
-        <v>125</v>
-      </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.709677419354</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L18" s="15">
-        <v>-47.222222222222</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.666666666666</v>
+        <v>-73.75</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.586894586894</v>
+        <v>-94.293478260869</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
         <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>11.111111111111</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>71.428571428571</v>
+        <v>40.625</v>
       </c>
       <c r="I19" s="14">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="J19" s="14">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K19" s="15">
-        <v>33.606557377049</v>
+        <v>36.641221374045</v>
       </c>
       <c r="L19" s="15">
-        <v>11.643835616438</v>
+        <v>9.146341463414</v>
       </c>
       <c r="M19" s="15">
-        <v>103.75</v>
+        <v>103.409090909091</v>
       </c>
       <c r="N19" s="15">
-        <v>5.844155844155</v>
+        <v>6.547619047619</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>14.285714285714</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>16</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I20" s="14">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.162790697674</v>
+        <v>-3.092783505154</v>
       </c>
       <c r="L20" s="15">
-        <v>1.190476190476</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>6.25</v>
+        <v>13.253012048192</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.219008264462</v>
+        <v>-90.811339198436</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>27.586206896551</v>
+        <v>3.030303030303</v>
       </c>
       <c r="F21" s="17">
         <v>134</v>
       </c>
       <c r="G21" s="17">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>39.583333333333</v>
+        <v>26.415094339622</v>
       </c>
       <c r="I21" s="17">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="J21" s="17">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="K21" s="18">
-        <v>11.688311688311</v>
+        <v>12.440191387559</v>
       </c>
       <c r="L21" s="18">
-        <v>2.137767220902</v>
+        <v>1.731601731601</v>
       </c>
       <c r="M21" s="18">
-        <v>21.813031161473</v>
+        <v>25.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.931330472103</v>
+        <v>-76.178408514951</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,16 +1201,16 @@
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
         <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>52.631578947368</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.884615384615</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I24" s="14">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="J24" s="14">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.249307479224</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.994011976047</v>
+        <v>-5.121293800539</v>
       </c>
       <c r="M24" s="15">
-        <v>90.588235294117</v>
+        <v>92.349726775956</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-18.181818181818</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-34</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="I25" s="14">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="J25" s="14">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.894736842105</v>
+        <v>-17.475728155339</v>
       </c>
       <c r="L25" s="15">
-        <v>-2.5</v>
+        <v>-4.494382022471</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>7.692307692307</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
         <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>18.421052631578</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I26" s="14">
+        <v>160</v>
+      </c>
+      <c r="J26" s="14">
         <v>154</v>
       </c>
-      <c r="J26" s="14">
-        <v>146</v>
-      </c>
       <c r="K26" s="15">
-        <v>5.479452054794</v>
+        <v>3.896103896103</v>
       </c>
       <c r="L26" s="15">
-        <v>4.761904761904</v>
+        <v>4.575163398692</v>
       </c>
       <c r="M26" s="15">
-        <v>12.408759124087</v>
+        <v>9.589041095890</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>40</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -902,28 +902,28 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N15" s="15">
         <v>-40</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>42.857142857142</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J16" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K16" s="15">
-        <v>12.962962962963</v>
+        <v>12.5</v>
       </c>
       <c r="L16" s="15">
-        <v>1.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.794871794871</v>
+        <v>-20.253164556962</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.180887372013</v>
+        <v>-79.207920792079</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.5</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
+        <v>29</v>
+      </c>
+      <c r="G17" s="14">
         <v>27</v>
       </c>
-      <c r="G17" s="14">
-        <v>23</v>
-      </c>
       <c r="H17" s="15">
-        <v>17.391304347826</v>
+        <v>7.407407407407</v>
       </c>
       <c r="I17" s="14">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J17" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K17" s="15">
-        <v>12.371134020618</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L17" s="15">
-        <v>9</v>
+        <v>5.504587155963</v>
       </c>
       <c r="M17" s="15">
-        <v>194.594594594595</v>
+        <v>194.871794871795</v>
       </c>
       <c r="N17" s="15">
-        <v>10.101010101010</v>
+        <v>0.877192982456</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-36.363636363636</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.153846153846</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.75</v>
+        <v>-72.619047619047</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.293478260869</v>
+        <v>-93.947368421052</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1066,31 +1066,31 @@
         <v>44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>40.625</v>
+        <v>92.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J19" s="14">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K19" s="15">
-        <v>36.641221374045</v>
+        <v>37.857142857142</v>
       </c>
       <c r="L19" s="15">
-        <v>9.146341463414</v>
+        <v>11.560693641618</v>
       </c>
       <c r="M19" s="15">
-        <v>103.409090909091</v>
+        <v>94.949494949494</v>
       </c>
       <c r="N19" s="15">
-        <v>6.547619047619</v>
+        <v>9.659090909090</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15">
-        <v>-18.181818181818</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>-3.225806451612</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J20" s="14">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.092783505154</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>4.081632653061</v>
       </c>
       <c r="M20" s="15">
-        <v>13.253012048192</v>
+        <v>14.606741573033</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.811339198436</v>
+        <v>-90.752493200362</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>3.030303030303</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="F21" s="17">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H21" s="18">
-        <v>26.415094339622</v>
+        <v>31.531531531531</v>
       </c>
       <c r="I21" s="17">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="J21" s="17">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="K21" s="18">
-        <v>12.440191387559</v>
+        <v>10.572687224669</v>
       </c>
       <c r="L21" s="18">
-        <v>1.731601731601</v>
+        <v>2.448979591836</v>
       </c>
       <c r="M21" s="18">
-        <v>25.333333333333</v>
+        <v>25.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.178408514951</v>
+        <v>-76.072449952335</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
+        <v>5</v>
+      </c>
+      <c r="J22" s="14">
         <v>4</v>
       </c>
-      <c r="J22" s="14">
-        <v>2</v>
-      </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.677419354838</v>
+        <v>89.473684210526</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.823529411764</v>
+        <v>30</v>
       </c>
       <c r="I24" s="14">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="J24" s="14">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.204081632653</v>
+        <v>-5.596107055961</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.121293800539</v>
+        <v>-1.272264631043</v>
       </c>
       <c r="M24" s="15">
-        <v>92.349726775956</v>
+        <v>94</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-12.5</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-13.725490196078</v>
+        <v>26.086956521739</v>
       </c>
       <c r="I25" s="14">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="J25" s="14">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.475728155339</v>
+        <v>-9.722222222222</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.494382022471</v>
+        <v>3.723404255319</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F26" s="14">
         <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>10.526315789473</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="I26" s="14">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J26" s="14">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="K26" s="15">
-        <v>3.896103896103</v>
+        <v>1.197604790419</v>
       </c>
       <c r="L26" s="15">
-        <v>4.575163398692</v>
+        <v>0.595238095238</v>
       </c>
       <c r="M26" s="15">
-        <v>9.589041095890</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,10 +1438,10 @@
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
         <v>15</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -881,8 +881,8 @@
       <c r="L14" s="15">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M15" s="15">
-        <v>-40</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>58.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J16" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K16" s="15">
-        <v>12.5</v>
+        <v>4.918032786885</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="M16" s="15">
-        <v>-20.253164556962</v>
+        <v>-22.891566265060</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.207920792079</v>
+        <v>-79.552715654952</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
         <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>7.407407407407</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J17" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K17" s="15">
-        <v>9.523809523809</v>
+        <v>9.734513274336</v>
       </c>
       <c r="L17" s="15">
-        <v>5.504587155963</v>
+        <v>5.982905982905</v>
       </c>
       <c r="M17" s="15">
-        <v>194.871794871795</v>
+        <v>175.555555555556</v>
       </c>
       <c r="N17" s="15">
-        <v>0.877192982456</v>
+        <v>-1.587301587301</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14">
+        <v>10</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>9</v>
-      </c>
-      <c r="G18" s="14">
-        <v>6</v>
-      </c>
-      <c r="H18" s="15">
-        <v>50</v>
-      </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.285714285714</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.902439024390</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="M18" s="15">
-        <v>-72.619047619047</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.947368421052</v>
+        <v>-93.765586034912</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>92.857142857142</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I19" s="14">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J19" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K19" s="15">
-        <v>37.857142857142</v>
+        <v>31.612903225806</v>
       </c>
       <c r="L19" s="15">
-        <v>11.560693641618</v>
+        <v>10.869565217391</v>
       </c>
       <c r="M19" s="15">
-        <v>94.949494949494</v>
+        <v>88.888888888888</v>
       </c>
       <c r="N19" s="15">
-        <v>9.659090909090</v>
+        <v>10.270270270270</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-42.857142857142</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F20" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G20" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.555555555555</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="I20" s="14">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="J20" s="14">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.108108108108</v>
+        <v>-3.389830508474</v>
       </c>
       <c r="L20" s="15">
-        <v>4.081632653061</v>
+        <v>9.615384615384</v>
       </c>
       <c r="M20" s="15">
-        <v>14.606741573033</v>
+        <v>21.276595744680</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.752493200362</v>
+        <v>-90.206185567010</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.888888888888</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G21" s="17">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="H21" s="18">
-        <v>31.531531531531</v>
+        <v>1.459854014598</v>
       </c>
       <c r="I21" s="17">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="J21" s="17">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="K21" s="18">
-        <v>10.572687224669</v>
+        <v>9.533468559837</v>
       </c>
       <c r="L21" s="18">
-        <v>2.448979591836</v>
+        <v>2.661596958174</v>
       </c>
       <c r="M21" s="18">
-        <v>25.5</v>
+        <v>26.463700234192</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.072449952335</v>
+        <v>-75.576662143826</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="E22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
+        <v>6</v>
+      </c>
+      <c r="J22" s="14">
         <v>5</v>
       </c>
-      <c r="J22" s="14">
-        <v>4</v>
-      </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>89.473684210526</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="14">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H24" s="15">
-        <v>30</v>
+        <v>14.893617021276</v>
       </c>
       <c r="I24" s="14">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="J24" s="14">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.596107055961</v>
+        <v>-7.568807339449</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.272264631043</v>
+        <v>-2.891566265060</v>
       </c>
       <c r="M24" s="15">
-        <v>94</v>
+        <v>92.822966507177</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>-84.210526315789</v>
       </c>
       <c r="F25" s="14">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>26.086956521739</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J25" s="14">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.722222222222</v>
+        <v>-15.319148936170</v>
       </c>
       <c r="L25" s="15">
-        <v>3.723404255319</v>
+        <v>-1.970443349753</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>18</v>
+      </c>
+      <c r="D26" s="14">
         <v>8</v>
       </c>
-      <c r="D26" s="14">
-        <v>13</v>
-      </c>
       <c r="E26" s="15">
-        <v>-38.461538461538</v>
+        <v>125</v>
       </c>
       <c r="F26" s="14">
+        <v>47</v>
+      </c>
+      <c r="G26" s="14">
         <v>42</v>
       </c>
-      <c r="G26" s="14">
-        <v>43</v>
-      </c>
       <c r="H26" s="15">
-        <v>-2.325581395348</v>
+        <v>11.904761904761</v>
       </c>
       <c r="I26" s="14">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="J26" s="14">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="K26" s="15">
-        <v>1.197604790419</v>
+        <v>6.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>0.595238095238</v>
+        <v>2.762430939226</v>
       </c>
       <c r="M26" s="15">
-        <v>8.333333333333</v>
+        <v>13.414634146341</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.222222222222</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>-22.222222222222</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1493,22 +1493,22 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1534,14 +1534,14 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-106pct.xlsx
+++ b/data/source/weekly/cs-en-us-106pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>3</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
         <v>-18.181818181818</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.142857142857</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
+        <v>68</v>
+      </c>
+      <c r="J16" s="14">
         <v>64</v>
       </c>
-      <c r="J16" s="14">
-        <v>61</v>
-      </c>
       <c r="K16" s="15">
-        <v>4.918032786885</v>
+        <v>6.25</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.859154929577</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.891566265060</v>
+        <v>-20</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.552715654952</v>
+        <v>-78.683385579937</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>12.5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G17" s="14">
         <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I17" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J17" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K17" s="15">
-        <v>9.734513274336</v>
+        <v>13.445378151260</v>
       </c>
       <c r="L17" s="15">
-        <v>5.982905982905</v>
+        <v>6.299212598425</v>
       </c>
       <c r="M17" s="15">
-        <v>175.555555555556</v>
+        <v>175.510204081633</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.587301587301</v>
+        <v>2.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.897435897435</v>
+        <v>-35</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.860465116279</v>
+        <v>-42.222222222222</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.588235294117</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.765586034912</v>
+        <v>-93.734939759036</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>9.523809523809</v>
+        <v>2.127659574468</v>
       </c>
       <c r="I19" s="14">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="J19" s="14">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K19" s="15">
-        <v>31.612903225806</v>
+        <v>27.810650887574</v>
       </c>
       <c r="L19" s="15">
-        <v>10.869565217391</v>
+        <v>11.917098445595</v>
       </c>
       <c r="M19" s="15">
-        <v>88.888888888888</v>
+        <v>83.050847457627</v>
       </c>
       <c r="N19" s="15">
-        <v>10.270270270270</v>
+        <v>10.204081632653</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>71.428571428571</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.128205128205</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I20" s="14">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J20" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.389830508474</v>
+        <v>-7.8125</v>
       </c>
       <c r="L20" s="15">
-        <v>9.615384615384</v>
+        <v>3.508771929824</v>
       </c>
       <c r="M20" s="15">
-        <v>21.276595744680</v>
+        <v>16.831683168316</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.206185567010</v>
+        <v>-90.343698854337</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.692307692307</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="F21" s="17">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G21" s="17">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H21" s="18">
-        <v>1.459854014598</v>
+        <v>-4.929577464788</v>
       </c>
       <c r="I21" s="17">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="J21" s="17">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="K21" s="18">
-        <v>9.533468559837</v>
+        <v>8.538899430740</v>
       </c>
       <c r="L21" s="18">
-        <v>2.661596958174</v>
+        <v>1.598579040852</v>
       </c>
       <c r="M21" s="18">
-        <v>26.463700234192</v>
+        <v>25.438596491228</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.576662143826</v>
+        <v>-75.195143104943</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1201,10 +1201,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-40</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G24" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H24" s="15">
-        <v>14.893617021276</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I24" s="14">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="J24" s="14">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.568807339449</v>
+        <v>-7.391304347826</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.891566265060</v>
+        <v>-2.517162471395</v>
       </c>
       <c r="M24" s="15">
-        <v>92.822966507177</v>
+        <v>91.031390134529</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-84.210526315789</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.142857142857</v>
+        <v>-5.084745762711</v>
       </c>
       <c r="I25" s="14">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="J25" s="14">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="K25" s="15">
-        <v>-15.319148936170</v>
+        <v>-14.859437751004</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.970443349753</v>
+        <v>-1.851851851851</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>125</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>11.904761904761</v>
+        <v>15</v>
       </c>
       <c r="I26" s="14">
+        <v>199</v>
+      </c>
+      <c r="J26" s="14">
         <v>186</v>
       </c>
-      <c r="J26" s="14">
-        <v>175</v>
-      </c>
       <c r="K26" s="15">
-        <v>6.285714285714</v>
+        <v>6.989247311827</v>
       </c>
       <c r="L26" s="15">
-        <v>2.762430939226</v>
+        <v>1.015228426395</v>
       </c>
       <c r="M26" s="15">
-        <v>13.414634146341</v>
+        <v>17.058823529411</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>7.692307692307</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
